--- a/excel/어떤 단어를 뭘로 틀렸는지 확인.xlsx
+++ b/excel/어떤 단어를 뭘로 틀렸는지 확인.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\classification-main\classification-main\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AC8BBD-9F02-4729-AAB1-EDFF11E3F084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB95EC1-2C78-419D-80E8-8DD3DC9372D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15255" yWindow="4200" windowWidth="20775" windowHeight="15315" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="global_conf_matrix" sheetId="4" r:id="rId1"/>
